--- a/casad_excel_template.xlsx
+++ b/casad_excel_template.xlsx
@@ -13237,7 +13237,7 @@
       </c>
       <c r="D57" s="363" t="n"/>
     </row>
-    <row r="58" ht="48.75" customFormat="1" customHeight="1" s="65">
+    <row r="58" ht="48.75" customHeight="1">
       <c r="A58" s="368" t="n"/>
       <c r="B58" s="74" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="D83" s="363" t="n"/>
     </row>
-    <row r="84" ht="60" customFormat="1" customHeight="1" s="66">
+    <row r="84" ht="60" customHeight="1">
       <c r="A84" s="250" t="inlineStr">
         <is>
           <t>(e)</t>
@@ -13809,7 +13809,7 @@
       </c>
       <c r="D91" s="363" t="n"/>
     </row>
-    <row r="92" ht="19.5" customFormat="1" customHeight="1" s="66" thickBot="1">
+    <row r="92" ht="19.5" customHeight="1" thickBot="1">
       <c r="A92" s="189" t="n">
         <v>8</v>
       </c>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="D92" s="372" t="n"/>
     </row>
-    <row r="93" customFormat="1" s="66">
+    <row r="93">
       <c r="A93" s="189" t="n">
         <v>9</v>
       </c>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="D93" s="363" t="n"/>
     </row>
-    <row r="94" ht="29.25" customFormat="1" customHeight="1" s="66" thickBot="1">
+    <row r="94" ht="29.25" customHeight="1" thickBot="1">
       <c r="A94" s="193" t="n">
         <v>10</v>
       </c>
@@ -14054,7 +14054,6 @@
     <col width="43.7109375" customWidth="1" style="1" min="3" max="3"/>
     <col width="8.85546875" customWidth="1" style="1" min="4" max="8"/>
     <col width="8.85546875" customWidth="1" style="46" min="9" max="9"/>
-    <col width="43.7109375" customWidth="1" style="1" min="10" max="10"/>
     <col width="8.85546875" customWidth="1" style="1" min="11" max="16384"/>
   </cols>
   <sheetData>
@@ -14075,11 +14074,6 @@
         </is>
       </c>
       <c r="D1" s="8" t="n"/>
-      <c r="J1" s="26" t="inlineStr">
-        <is>
-          <t>Perticulars as per record</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="67" t="n">
@@ -14092,9 +14086,6 @@
         <v>3</v>
       </c>
       <c r="D2" s="9" t="n"/>
-      <c r="J2" s="27" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
@@ -14107,7 +14098,6 @@
       </c>
       <c r="C3" s="79" t="n"/>
       <c r="D3" s="10" t="n"/>
-      <c r="J3" s="79" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="28" t="n">
@@ -14123,10 +14113,6 @@
         <v/>
       </c>
       <c r="D4" s="10" t="n"/>
-      <c r="J4" s="79">
-        <f>'Appendix-A'!J4</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="n">
@@ -14142,10 +14128,6 @@
         <v/>
       </c>
       <c r="D5" s="10" t="n"/>
-      <c r="J5" s="79">
-        <f>'Appendix-A'!J5</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="28" t="n">
@@ -14161,10 +14143,6 @@
         <v/>
       </c>
       <c r="D6" s="10" t="n"/>
-      <c r="J6" s="79">
-        <f>'Appendix-A'!J6</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
@@ -14182,10 +14160,6 @@
         <v/>
       </c>
       <c r="D7" s="10" t="n"/>
-      <c r="J7" s="79">
-        <f>'Appendix-A'!J7</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
@@ -14203,10 +14177,6 @@
         <v/>
       </c>
       <c r="D8" s="10" t="n"/>
-      <c r="J8" s="79">
-        <f>'Appendix-A'!J8</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="28" t="inlineStr">
@@ -14224,10 +14194,6 @@
         <v/>
       </c>
       <c r="D9" s="10" t="n"/>
-      <c r="J9" s="79">
-        <f>'Appendix-A'!J9</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="28" t="inlineStr">
@@ -14245,10 +14211,6 @@
         <v/>
       </c>
       <c r="D10" s="10" t="n"/>
-      <c r="J10" s="79">
-        <f>'Appendix-A'!J12</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
@@ -14264,10 +14226,6 @@
         <v/>
       </c>
       <c r="D11" s="10" t="n"/>
-      <c r="J11" s="79">
-        <f>J6</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
@@ -14282,9 +14240,6 @@
         <v>45943</v>
       </c>
       <c r="D12" s="10" t="n"/>
-      <c r="J12" s="80" t="n">
-        <v>45940</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
@@ -14297,7 +14252,6 @@
       </c>
       <c r="C13" s="79" t="n"/>
       <c r="D13" s="10" t="n"/>
-      <c r="J13" s="79" t="n"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="28" t="n">
@@ -14315,12 +14269,6 @@
         </is>
       </c>
       <c r="D14" s="10" t="n"/>
-      <c r="J14" s="79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pot-holes (Existing Approach)
-</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="28" t="n">
@@ -14337,11 +14285,6 @@
         </is>
       </c>
       <c r="D15" s="2" t="n"/>
-      <c r="J15" s="79" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="28" t="n">
@@ -14358,11 +14301,6 @@
         </is>
       </c>
       <c r="D16" s="2" t="n"/>
-      <c r="J16" s="79" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="28" t="n">
@@ -14379,11 +14317,6 @@
         </is>
       </c>
       <c r="D17" s="10" t="n"/>
-      <c r="J17" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="28" t="n">
@@ -14400,11 +14333,6 @@
         </is>
       </c>
       <c r="D18" s="10" t="n"/>
-      <c r="J18" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="28" t="n">
@@ -14421,11 +14349,6 @@
         </is>
       </c>
       <c r="D19" s="10" t="n"/>
-      <c r="J19" s="79" t="inlineStr">
-        <is>
-          <t>The existing approach is not accessible due to small huts constructed by local residents, and the opposite side is inaccessible because of dense vegetation.</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
@@ -14442,11 +14365,6 @@
         </is>
       </c>
       <c r="D20" s="10" t="n"/>
-      <c r="J20" s="79" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="28" t="n">
@@ -14463,11 +14381,6 @@
         </is>
       </c>
       <c r="D21" s="2" t="n"/>
-      <c r="J21" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="45.75" customHeight="1" thickBot="1">
       <c r="A22" s="20" t="n">
@@ -14484,11 +14397,6 @@
         </is>
       </c>
       <c r="D22" s="2" t="n"/>
-      <c r="J22" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="90" customHeight="1">
       <c r="A23" s="22" t="n">
@@ -14505,11 +14413,6 @@
         </is>
       </c>
       <c r="D23" s="3" t="n"/>
-      <c r="J23" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="24" ht="60" customHeight="1">
       <c r="A24" s="28" t="n">
@@ -14526,11 +14429,6 @@
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
-      <c r="J24" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="28" t="n">
@@ -14547,11 +14445,6 @@
         </is>
       </c>
       <c r="D25" s="3" t="n"/>
-      <c r="J25" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="n">
@@ -14568,11 +14461,6 @@
         </is>
       </c>
       <c r="D26" s="2" t="n"/>
-      <c r="J26" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="28" t="n">
@@ -14589,11 +14477,6 @@
         </is>
       </c>
       <c r="D27" s="2" t="n"/>
-      <c r="J27" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
@@ -14610,11 +14493,6 @@
         </is>
       </c>
       <c r="D28" s="2" t="n"/>
-      <c r="J28" s="79" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="28" t="n">
@@ -14631,11 +14509,6 @@
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
-      <c r="J29" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="28" t="n">
@@ -14652,11 +14525,6 @@
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
-      <c r="J30" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="28" t="n">
@@ -14673,11 +14541,6 @@
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
-      <c r="J31" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="A32" s="28" t="n">
@@ -14694,11 +14557,6 @@
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
-      <c r="J32" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="28" t="n">
@@ -14715,11 +14573,6 @@
         </is>
       </c>
       <c r="D33" s="10" t="n"/>
-      <c r="J33" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="28" t="n">
@@ -14736,11 +14589,6 @@
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
-      <c r="J34" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="28" t="n">
@@ -14757,11 +14605,6 @@
         </is>
       </c>
       <c r="D35" s="10" t="n"/>
-      <c r="J35" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
@@ -14778,11 +14621,6 @@
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
-      <c r="J36" s="79" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="28" t="n">
@@ -14799,11 +14637,6 @@
         </is>
       </c>
       <c r="D37" s="10" t="n"/>
-      <c r="J37" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="28" t="n">
@@ -14820,11 +14653,6 @@
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
-      <c r="J38" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="28" t="n">
@@ -14841,11 +14669,6 @@
         </is>
       </c>
       <c r="D39" s="10" t="n"/>
-      <c r="J39" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="28" t="n">
@@ -14862,11 +14685,6 @@
         </is>
       </c>
       <c r="D40" s="10" t="n"/>
-      <c r="J40" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="28" t="n">
@@ -14883,11 +14701,6 @@
         </is>
       </c>
       <c r="D41" s="10" t="n"/>
-      <c r="J41" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="29.25" customHeight="1">
       <c r="A42" s="15" t="n">
@@ -14905,11 +14718,6 @@
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
-      <c r="J42" s="81" t="inlineStr">
-        <is>
-          <t>Refer Table  1 and 2</t>
-        </is>
-      </c>
     </row>
     <row r="43" ht="60" customHeight="1">
       <c r="A43" s="28" t="n">
@@ -14926,11 +14734,6 @@
         </is>
       </c>
       <c r="D43" s="10" t="n"/>
-      <c r="J43" s="79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Clogged Weep Holes </t>
-        </is>
-      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="28" t="n">
@@ -14947,11 +14750,6 @@
         </is>
       </c>
       <c r="D44" s="10" t="n"/>
-      <c r="J44" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="28" t="n">
@@ -14968,11 +14766,6 @@
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
-      <c r="J45" s="79" t="inlineStr">
-        <is>
-          <t>Minor cracks on Clossing Wall</t>
-        </is>
-      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" thickBot="1">
       <c r="A46" s="20" t="n">
@@ -14989,11 +14782,6 @@
         </is>
       </c>
       <c r="D46" s="10" t="n"/>
-      <c r="J46" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="n">
@@ -15006,7 +14794,6 @@
       </c>
       <c r="C47" s="83" t="n"/>
       <c r="D47" s="10" t="n"/>
-      <c r="J47" s="83" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="28" t="n">
@@ -15023,11 +14810,6 @@
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
-      <c r="J48" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="28" t="inlineStr">
@@ -15046,11 +14828,6 @@
         </is>
       </c>
       <c r="D49" s="10" t="n"/>
-      <c r="J49" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="28" t="inlineStr">
@@ -15069,11 +14846,6 @@
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
-      <c r="J50" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="51" ht="45" customHeight="1">
       <c r="A51" s="28" t="inlineStr">
@@ -15092,11 +14864,6 @@
         </is>
       </c>
       <c r="D51" s="10" t="n"/>
-      <c r="J51" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="28" t="inlineStr">
@@ -15115,11 +14882,6 @@
         </is>
       </c>
       <c r="D52" s="10" t="n"/>
-      <c r="J52" s="79" t="inlineStr">
-        <is>
-          <t>Crack/Damage in pedestal and Sesmic Arrester</t>
-        </is>
-      </c>
     </row>
     <row r="53" ht="45" customHeight="1">
       <c r="A53" s="28" t="inlineStr">
@@ -15138,11 +14900,6 @@
         </is>
       </c>
       <c r="D53" s="10" t="n"/>
-      <c r="J53" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="28" t="inlineStr">
@@ -15161,11 +14918,6 @@
         </is>
       </c>
       <c r="D54" s="10" t="n"/>
-      <c r="J54" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="28" t="n">
@@ -15182,11 +14934,6 @@
         </is>
       </c>
       <c r="D55" s="10" t="n"/>
-      <c r="J55" s="79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="28" t="inlineStr">
@@ -15205,11 +14952,6 @@
         </is>
       </c>
       <c r="D56" s="10" t="n"/>
-      <c r="J56" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="28" t="inlineStr">
@@ -15228,11 +14970,6 @@
         </is>
       </c>
       <c r="D57" s="10" t="n"/>
-      <c r="J57" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="28" t="inlineStr">
@@ -15251,11 +14988,6 @@
         </is>
       </c>
       <c r="D58" s="10" t="n"/>
-      <c r="J58" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
@@ -15272,7 +15004,6 @@
         </is>
       </c>
       <c r="D59" s="10" t="n"/>
-      <c r="J59" s="79" t="n"/>
     </row>
     <row r="60" ht="81.75" customHeight="1">
       <c r="A60" s="28" t="n">
@@ -15288,10 +15019,6 @@
         <v/>
       </c>
       <c r="D60" s="10" t="n"/>
-      <c r="J60" s="79">
-        <f>'Appendix-A'!J43</f>
-        <v/>
-      </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="28" t="inlineStr">
@@ -15310,11 +15037,6 @@
         </is>
       </c>
       <c r="D61" s="10" t="n"/>
-      <c r="J61" s="79" t="inlineStr">
-        <is>
-          <t>Spalling in Solid slab (Gomtipur Side road)</t>
-        </is>
-      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="28" t="inlineStr">
@@ -15333,11 +15055,6 @@
         </is>
       </c>
       <c r="D62" s="10" t="n"/>
-      <c r="J62" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="28" t="inlineStr">
@@ -15356,11 +15073,6 @@
         </is>
       </c>
       <c r="D63" s="10" t="n"/>
-      <c r="J63" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="28" t="inlineStr">
@@ -15379,11 +15091,6 @@
         </is>
       </c>
       <c r="D64" s="10" t="n"/>
-      <c r="J64" s="79" t="inlineStr">
-        <is>
-          <t>Longitudinal &amp; Transverse Expansion Joint Damage</t>
-        </is>
-      </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="28" t="inlineStr">
@@ -15402,11 +15109,6 @@
         </is>
       </c>
       <c r="D65" s="10" t="n"/>
-      <c r="J65" s="79" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="28" t="inlineStr">
@@ -15425,11 +15127,6 @@
         </is>
       </c>
       <c r="D66" s="10" t="n"/>
-      <c r="J66" s="84" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="67" ht="45" customHeight="1">
       <c r="A67" s="28" t="inlineStr">
@@ -15448,11 +15145,6 @@
         </is>
       </c>
       <c r="D67" s="10" t="n"/>
-      <c r="J67" s="84" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="28" t="inlineStr">
@@ -15471,11 +15163,6 @@
         </is>
       </c>
       <c r="D68" s="10" t="n"/>
-      <c r="J68" s="84" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="69" ht="30.75" customHeight="1" thickBot="1">
       <c r="A69" s="20" t="inlineStr">
@@ -15494,11 +15181,6 @@
         </is>
       </c>
       <c r="D69" s="10" t="n"/>
-      <c r="J69" s="79" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="22" t="n">
@@ -15515,11 +15197,6 @@
         </is>
       </c>
       <c r="D70" s="10" t="n"/>
-      <c r="J70" s="83" t="inlineStr">
-        <is>
-          <t>Railway Portion</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="28" t="inlineStr">
@@ -15538,11 +15215,6 @@
         </is>
       </c>
       <c r="D71" s="10" t="n"/>
-      <c r="J71" s="79" t="inlineStr">
-        <is>
-          <t>Fadded</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="28" t="inlineStr">
@@ -15561,11 +15233,6 @@
         </is>
       </c>
       <c r="D72" s="10" t="n"/>
-      <c r="J72" s="79" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="28" t="inlineStr">
@@ -15584,11 +15251,6 @@
         </is>
       </c>
       <c r="D73" s="10" t="n"/>
-      <c r="J73" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="28" t="inlineStr">
@@ -15607,11 +15269,6 @@
         </is>
       </c>
       <c r="D74" s="10" t="n"/>
-      <c r="J74" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="75" ht="77.25" customHeight="1">
       <c r="A75" s="28" t="inlineStr">
@@ -15630,11 +15287,6 @@
         </is>
       </c>
       <c r="D75" s="10" t="n"/>
-      <c r="J75" s="79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Looseness of a few bolts </t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="28" t="inlineStr">
@@ -15653,11 +15305,6 @@
         </is>
       </c>
       <c r="D76" s="10" t="n"/>
-      <c r="J76" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="28" t="inlineStr">
@@ -15676,11 +15323,6 @@
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
-      <c r="J77" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="78" ht="45" customHeight="1">
       <c r="A78" s="28" t="inlineStr">
@@ -15699,11 +15341,6 @@
         </is>
       </c>
       <c r="D78" s="10" t="n"/>
-      <c r="J78" s="79" t="inlineStr">
-        <is>
-          <t>Drainage Hole clogged</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="28" t="n">
@@ -15720,11 +15357,6 @@
         </is>
       </c>
       <c r="D79" s="10" t="n"/>
-      <c r="J79" s="81" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="28" t="inlineStr">
@@ -15743,11 +15375,6 @@
         </is>
       </c>
       <c r="D80" s="10" t="n"/>
-      <c r="J80" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="28" t="inlineStr">
@@ -15766,11 +15393,6 @@
         </is>
       </c>
       <c r="D81" s="10" t="n"/>
-      <c r="J81" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="28" t="inlineStr">
@@ -15789,11 +15411,6 @@
         </is>
       </c>
       <c r="D82" s="10" t="n"/>
-      <c r="J82" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="28" t="inlineStr">
@@ -15812,11 +15429,6 @@
         </is>
       </c>
       <c r="D83" s="10" t="n"/>
-      <c r="J83" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="28" t="inlineStr">
@@ -15835,11 +15447,6 @@
         </is>
       </c>
       <c r="D84" s="10" t="n"/>
-      <c r="J84" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="28" t="inlineStr">
@@ -15858,11 +15465,6 @@
         </is>
       </c>
       <c r="D85" s="10" t="n"/>
-      <c r="J85" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="28" t="n">
@@ -15879,11 +15481,6 @@
         </is>
       </c>
       <c r="D86" s="10" t="n"/>
-      <c r="J86" s="81" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="28" t="inlineStr">
@@ -15902,11 +15499,6 @@
         </is>
       </c>
       <c r="D87" s="10" t="n"/>
-      <c r="J87" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="88" ht="45" customHeight="1">
       <c r="A88" s="28" t="inlineStr">
@@ -15925,11 +15517,6 @@
         </is>
       </c>
       <c r="D88" s="10" t="n"/>
-      <c r="J88" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="28" t="inlineStr">
@@ -15948,11 +15535,6 @@
         </is>
       </c>
       <c r="D89" s="10" t="n"/>
-      <c r="J89" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" thickBot="1">
       <c r="A90" s="20" t="inlineStr">
@@ -15971,11 +15553,6 @@
         </is>
       </c>
       <c r="D90" s="10" t="n"/>
-      <c r="J90" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="13" t="n">
@@ -15988,7 +15565,6 @@
       </c>
       <c r="C91" s="83" t="n"/>
       <c r="D91" s="10" t="n"/>
-      <c r="J91" s="83" t="n"/>
     </row>
     <row r="92" ht="45" customHeight="1">
       <c r="A92" s="28" t="n">
@@ -16005,11 +15581,6 @@
         </is>
       </c>
       <c r="D92" s="10" t="n"/>
-      <c r="J92" s="79" t="inlineStr">
-        <is>
-          <t>Longitudinal and Transverse Expansion Joint Damage</t>
-        </is>
-      </c>
     </row>
     <row r="93" ht="75" customHeight="1">
       <c r="A93" s="28" t="n">
@@ -16026,11 +15597,6 @@
         </is>
       </c>
       <c r="D93" s="10" t="n"/>
-      <c r="J93" s="79" t="inlineStr">
-        <is>
-          <t>Not Accessible</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="28" t="n">
@@ -16047,11 +15613,6 @@
         </is>
       </c>
       <c r="D94" s="10" t="n"/>
-      <c r="J94" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="28" t="n">
@@ -16068,11 +15629,6 @@
         </is>
       </c>
       <c r="D95" s="10" t="n"/>
-      <c r="J95" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="28" t="n">
@@ -16089,11 +15645,6 @@
         </is>
       </c>
       <c r="D96" s="10" t="n"/>
-      <c r="J96" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="28" t="n">
@@ -16110,11 +15661,6 @@
         </is>
       </c>
       <c r="D97" s="10" t="n"/>
-      <c r="J97" s="79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="28" t="n">
@@ -16131,11 +15677,6 @@
         </is>
       </c>
       <c r="D98" s="10" t="n"/>
-      <c r="J98" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="28" t="n">
@@ -16152,11 +15693,6 @@
         </is>
       </c>
       <c r="D99" s="10" t="n"/>
-      <c r="J99" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
@@ -16173,11 +15709,6 @@
         </is>
       </c>
       <c r="D100" s="10" t="n"/>
-      <c r="J100" s="79" t="inlineStr">
-        <is>
-          <t>Bituminous</t>
-        </is>
-      </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="28" t="n">
@@ -16195,11 +15726,6 @@
         </is>
       </c>
       <c r="D101" s="10" t="n"/>
-      <c r="J101" s="79" t="inlineStr">
-        <is>
-          <t>Pot-holes</t>
-        </is>
-      </c>
     </row>
     <row r="102" ht="45" customHeight="1">
       <c r="A102" s="28" t="n">
@@ -16216,11 +15742,6 @@
         </is>
       </c>
       <c r="D102" s="10" t="n"/>
-      <c r="J102" s="79" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="n">
@@ -16233,7 +15754,6 @@
       </c>
       <c r="C103" s="79" t="n"/>
       <c r="D103" s="10" t="n"/>
-      <c r="J103" s="79" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="28" t="n">
@@ -16250,11 +15770,6 @@
         </is>
       </c>
       <c r="D104" s="10" t="n"/>
-      <c r="J104" s="79" t="inlineStr">
-        <is>
-          <t>few clogged</t>
-        </is>
-      </c>
     </row>
     <row r="105" ht="45" customHeight="1">
       <c r="A105" s="28" t="n">
@@ -16271,11 +15786,6 @@
         </is>
       </c>
       <c r="D105" s="10" t="n"/>
-      <c r="J105" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="28" t="n">
@@ -16292,11 +15802,6 @@
         </is>
       </c>
       <c r="D106" s="10" t="n"/>
-      <c r="J106" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="28" t="n">
@@ -16313,11 +15818,6 @@
         </is>
       </c>
       <c r="D107" s="10" t="n"/>
-      <c r="J107" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1" thickBot="1">
       <c r="A108" s="20" t="n">
@@ -16334,11 +15834,6 @@
         </is>
       </c>
       <c r="D108" s="10" t="n"/>
-      <c r="J108" s="82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="13" t="n">
@@ -16351,7 +15846,6 @@
       </c>
       <c r="C109" s="83" t="n"/>
       <c r="D109" s="10" t="n"/>
-      <c r="J109" s="83" t="n"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="28" t="n">
@@ -16368,11 +15862,6 @@
         </is>
       </c>
       <c r="D110" s="10" t="n"/>
-      <c r="J110" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="28" t="n">
@@ -16389,11 +15878,6 @@
         </is>
       </c>
       <c r="D111" s="10" t="n"/>
-      <c r="J111" s="79" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="28" t="n">
@@ -16410,11 +15894,6 @@
         </is>
       </c>
       <c r="D112" s="10" t="n"/>
-      <c r="J112" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="n">
@@ -16427,7 +15906,6 @@
       </c>
       <c r="C113" s="79" t="n"/>
       <c r="D113" s="10" t="n"/>
-      <c r="J113" s="79" t="n"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="28" t="n">
@@ -16444,11 +15922,6 @@
         </is>
       </c>
       <c r="D114" s="10" t="n"/>
-      <c r="J114" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="28" t="n">
@@ -16465,11 +15938,6 @@
         </is>
       </c>
       <c r="D115" s="10" t="n"/>
-      <c r="J115" s="84" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="28" t="n">
@@ -16486,11 +15954,6 @@
         </is>
       </c>
       <c r="D116" s="10" t="n"/>
-      <c r="J116" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="15" t="n">
@@ -16503,7 +15966,6 @@
       </c>
       <c r="C117" s="79" t="n"/>
       <c r="D117" s="10" t="n"/>
-      <c r="J117" s="79" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="28" t="n">
@@ -16520,11 +15982,6 @@
         </is>
       </c>
       <c r="D118" s="10" t="n"/>
-      <c r="J118" s="84" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="28" t="n">
@@ -16541,11 +15998,6 @@
         </is>
       </c>
       <c r="D119" s="10" t="n"/>
-      <c r="J119" s="84" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="28" t="n">
@@ -16562,11 +16014,6 @@
         </is>
       </c>
       <c r="D120" s="10" t="n"/>
-      <c r="J120" s="79" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="28" t="n">
@@ -16583,11 +16030,6 @@
         </is>
       </c>
       <c r="D121" s="10" t="n"/>
-      <c r="J121" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="15" t="n">
@@ -16604,11 +16046,6 @@
         </is>
       </c>
       <c r="D122" s="10" t="n"/>
-      <c r="J122" s="79" t="inlineStr">
-        <is>
-          <t>Data not Available</t>
-        </is>
-      </c>
     </row>
     <row r="123" ht="45" customHeight="1">
       <c r="A123" s="28" t="n">
@@ -16625,11 +16062,6 @@
         </is>
       </c>
       <c r="D123" s="10" t="n"/>
-      <c r="J123" s="79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="n">
@@ -16642,7 +16074,6 @@
       </c>
       <c r="C124" s="79" t="n"/>
       <c r="D124" s="10" t="n"/>
-      <c r="J124" s="79" t="n"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="28" t="n">
@@ -16659,11 +16090,6 @@
         </is>
       </c>
       <c r="D125" s="10" t="n"/>
-      <c r="J125" s="84" t="inlineStr">
-        <is>
-          <t>Absent</t>
-        </is>
-      </c>
     </row>
     <row r="126" ht="42.75" customHeight="1">
       <c r="A126" s="15" t="n">
@@ -16680,11 +16106,6 @@
         </is>
       </c>
       <c r="D126" s="10" t="n"/>
-      <c r="J126" s="79" t="inlineStr">
-        <is>
-          <t>Data not Available</t>
-        </is>
-      </c>
     </row>
     <row r="127" hidden="1" ht="21.2" customFormat="1" customHeight="1" s="48">
       <c r="A127" s="15" t="n">
@@ -16702,11 +16123,6 @@
       </c>
       <c r="D127" s="11" t="n"/>
       <c r="I127" s="47" t="n"/>
-      <c r="J127" s="79" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
     </row>
     <row r="128" hidden="1" ht="36.75" customHeight="1">
       <c r="A128" s="15" t="n">
@@ -16723,11 +16139,6 @@
         </is>
       </c>
       <c r="D128" s="10" t="n"/>
-      <c r="J128" s="79" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
     </row>
     <row r="129" ht="173.25" customHeight="1" thickBot="1">
       <c r="A129" s="16" t="n">
@@ -16754,25 +16165,11 @@
         </is>
       </c>
       <c r="D129" s="10" t="n"/>
-      <c r="J129" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Repair works Required as follow,
-1. Expansion Joint
-2. Minor crack in Retaining wall
-3. Looseness of Bolts
-4. Painting on Corrosive Steel Member Truss
-5. Wearing Surface
-6. Removal of Vegitation
-7. Repairing required in staircase foundation-pedestal
-</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="12" t="n"/>
       <c r="B130" s="12" t="n"/>
       <c r="C130" s="12" t="n"/>
-      <c r="J130" s="12" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
